--- a/ClientExcel/Game/UIFormGroup.xlsx
+++ b/ClientExcel/Game/UIFormGroup.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>#</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>策划备注</t>
+  </si>
+  <si>
+    <t>界面组编号枚举名</t>
   </si>
   <si>
     <t>组名称</t>
@@ -1033,8 +1036,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="22.875" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="22.875" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="16384" width="22.875" style="1" customWidth="1"/>
   </cols>
@@ -1047,35 +1050,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1091,71 +1094,89 @@
       <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="2:6">
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="2:6">
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="2:6">
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="1">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" spans="2:6">
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="4:4">
+    <row r="9" spans="4:5">
       <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="4:4">
+    <row r="10" spans="4:5">
       <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="4:4">
+    <row r="11" spans="4:5">
       <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
